--- a/pds_admin_raj/Backend/Backend/Data_1.xlsx
+++ b/pds_admin_raj/Backend/Backend/Data_1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="1494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3588" uniqueCount="1493">
   <si>
     <t>State Name</t>
   </si>
@@ -4097,9 +4097,6 @@
   </si>
   <si>
     <t>Owned</t>
-  </si>
-  <si>
-    <t>hired</t>
   </si>
   <si>
     <t>Hired</t>
@@ -13698,10 +13695,10 @@
         <v>1358</v>
       </c>
       <c r="F2" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2">
         <v>358747.86</v>
@@ -13724,10 +13721,10 @@
         <v>1358</v>
       </c>
       <c r="F3" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H3">
         <v>309842.86</v>
@@ -13750,10 +13747,10 @@
         <v>1358</v>
       </c>
       <c r="F4" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G4" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H4">
         <v>267166.53</v>
@@ -13779,7 +13776,7 @@
         <v>502</v>
       </c>
       <c r="G5" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H5">
         <v>79296.11</v>
@@ -13828,10 +13825,10 @@
         <v>1358</v>
       </c>
       <c r="F7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G7" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H7">
         <v>201228.51</v>
@@ -13857,7 +13854,7 @@
         <v>558</v>
       </c>
       <c r="G8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H8">
         <v>45384</v>
@@ -13880,7 +13877,7 @@
         <v>1358</v>
       </c>
       <c r="F9" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G9" t="s">
         <v>872</v>
@@ -13903,10 +13900,10 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F10" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G10" t="s">
         <v>872</v>
@@ -13929,10 +13926,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F11" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G11" t="s">
         <v>872</v>
@@ -13958,10 +13955,10 @@
         <v>1358</v>
       </c>
       <c r="F12" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G12" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H12">
         <v>36995.45</v>
@@ -13981,7 +13978,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="s">
         <v>678</v>
@@ -14007,13 +14004,13 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F14" t="s">
         <v>565</v>
       </c>
       <c r="G14" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H14">
         <v>15000</v>
@@ -14033,13 +14030,13 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F15" t="s">
         <v>565</v>
       </c>
       <c r="G15" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H15">
         <v>4335.54</v>
@@ -14059,13 +14056,13 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F16" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G16" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H16">
         <v>61600</v>
@@ -14085,13 +14082,13 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F17" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G17" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H17">
         <v>65800</v>
@@ -14111,10 +14108,10 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F18" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G18" t="s">
         <v>872</v>
@@ -14137,10 +14134,10 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F19" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G19" t="s">
         <v>777</v>
@@ -14163,10 +14160,10 @@
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F20" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G20" t="s">
         <v>793</v>
@@ -14189,7 +14186,7 @@
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F21" t="s">
         <v>474</v>
@@ -14215,7 +14212,7 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F22" t="s">
         <v>680</v>
@@ -14241,13 +14238,13 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F23" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G23" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H23">
         <v>22500</v>
@@ -14270,7 +14267,7 @@
         <v>1358</v>
       </c>
       <c r="F24" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G24" t="s">
         <v>749</v>
@@ -14293,7 +14290,7 @@
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F25" t="s">
         <v>476</v>
@@ -14319,7 +14316,7 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F26" t="s">
         <v>483</v>
@@ -14345,10 +14342,10 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F27" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G27" t="s">
         <v>744</v>
@@ -14400,10 +14397,10 @@
         <v>1358</v>
       </c>
       <c r="F29" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G29" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H29">
         <v>189590</v>
@@ -14423,13 +14420,13 @@
         <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F30" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G30" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H30">
         <v>121220</v>
@@ -14449,13 +14446,13 @@
         <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F31" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G31" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H31">
         <v>45540</v>
@@ -14478,10 +14475,10 @@
         <v>1358</v>
       </c>
       <c r="F32" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G32" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H32">
         <v>119870</v>
@@ -14501,13 +14498,13 @@
         <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F33" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G33" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H33">
         <v>18040</v>
@@ -14527,13 +14524,13 @@
         <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F34" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G34" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H34">
         <v>30840</v>
@@ -14553,10 +14550,10 @@
         <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F35" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G35" t="s">
         <v>920</v>
@@ -14579,13 +14576,13 @@
         <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F36" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G36" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H36">
         <v>28000</v>
@@ -14605,7 +14602,7 @@
         <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F37" t="s">
         <v>476</v>
@@ -14631,7 +14628,7 @@
         <v>35</v>
       </c>
       <c r="E38" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F38" t="s">
         <v>664</v>
@@ -14657,13 +14654,13 @@
         <v>36</v>
       </c>
       <c r="E39" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F39" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G39" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H39">
         <v>99000</v>
@@ -14683,7 +14680,7 @@
         <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F40" t="s">
         <v>479</v>
@@ -14709,13 +14706,13 @@
         <v>38</v>
       </c>
       <c r="E41" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F41" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G41" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H41">
         <v>151600</v>
@@ -14787,10 +14784,10 @@
         <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F44" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G44" t="s">
         <v>982</v>
@@ -14813,13 +14810,13 @@
         <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F45" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G45" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H45">
         <v>660</v>
@@ -14842,7 +14839,7 @@
         <v>1358</v>
       </c>
       <c r="F46" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G46" t="s">
         <v>793</v>
@@ -14920,7 +14917,7 @@
         <v>1358</v>
       </c>
       <c r="F49" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G49" t="s">
         <v>853</v>
@@ -14943,10 +14940,10 @@
         <v>47</v>
       </c>
       <c r="E50" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F50" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G50" t="s">
         <v>853</v>
@@ -14972,10 +14969,10 @@
         <v>1358</v>
       </c>
       <c r="F51" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G51" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H51">
         <v>63240</v>
@@ -14995,13 +14992,13 @@
         <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F52" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G52" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H52">
         <v>89960</v>
@@ -15021,7 +15018,7 @@
         <v>50</v>
       </c>
       <c r="E53" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F53" t="s">
         <v>479</v>
@@ -15047,13 +15044,13 @@
         <v>51</v>
       </c>
       <c r="E54" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F54" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G54" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H54">
         <v>28360</v>
@@ -15073,10 +15070,10 @@
         <v>52</v>
       </c>
       <c r="E55" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F55" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G55" t="s">
         <v>940</v>
@@ -15099,13 +15096,13 @@
         <v>53</v>
       </c>
       <c r="E56" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F56" t="s">
         <v>666</v>
       </c>
       <c r="G56" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H56">
         <v>20160</v>
@@ -15125,13 +15122,13 @@
         <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F57" t="s">
         <v>666</v>
       </c>
       <c r="G57" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H57">
         <v>20180</v>
@@ -15151,10 +15148,10 @@
         <v>55</v>
       </c>
       <c r="E58" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F58" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G58" t="s">
         <v>932</v>
@@ -15183,7 +15180,7 @@
         <v>584</v>
       </c>
       <c r="G59" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H59">
         <v>152400</v>
@@ -15203,7 +15200,7 @@
         <v>57</v>
       </c>
       <c r="E60" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F60" t="s">
         <v>580</v>
@@ -15229,10 +15226,10 @@
         <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F61" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G61" t="s">
         <v>914</v>
@@ -15255,10 +15252,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F62" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G62" t="s">
         <v>914</v>
@@ -15284,10 +15281,10 @@
         <v>1358</v>
       </c>
       <c r="F63" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="G63" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H63">
         <v>68670</v>
@@ -15307,10 +15304,10 @@
         <v>61</v>
       </c>
       <c r="E64" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F64" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G64" t="s">
         <v>883</v>
@@ -15336,7 +15333,7 @@
         <v>1358</v>
       </c>
       <c r="F65" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G65" t="s">
         <v>830</v>
@@ -15359,10 +15356,10 @@
         <v>63</v>
       </c>
       <c r="E66" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F66" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G66" t="s">
         <v>833</v>
@@ -15385,10 +15382,10 @@
         <v>64</v>
       </c>
       <c r="E67" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F67" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G67" t="s">
         <v>853</v>
@@ -15411,13 +15408,13 @@
         <v>65</v>
       </c>
       <c r="E68" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F68" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="G68" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H68">
         <v>92400</v>
@@ -15437,7 +15434,7 @@
         <v>66</v>
       </c>
       <c r="E69" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F69" t="s">
         <v>479</v>
@@ -15463,7 +15460,7 @@
         <v>67</v>
       </c>
       <c r="E70" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F70" t="s">
         <v>479</v>
@@ -15489,10 +15486,10 @@
         <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F71" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G71" t="s">
         <v>914</v>
@@ -15515,13 +15512,13 @@
         <v>69</v>
       </c>
       <c r="E72" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F72" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G72" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H72">
         <v>57400</v>
@@ -15541,10 +15538,10 @@
         <v>70</v>
       </c>
       <c r="E73" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F73" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G73" t="s">
         <v>833</v>
@@ -15567,10 +15564,10 @@
         <v>71</v>
       </c>
       <c r="E74" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F74" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="G74" t="s">
         <v>858</v>
@@ -15593,13 +15590,13 @@
         <v>72</v>
       </c>
       <c r="E75" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F75" t="s">
         <v>736</v>
       </c>
       <c r="G75" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H75">
         <v>22000</v>
@@ -15619,13 +15616,13 @@
         <v>73</v>
       </c>
       <c r="E76" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F76" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G76" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H76">
         <v>250560</v>
@@ -15645,13 +15642,13 @@
         <v>74</v>
       </c>
       <c r="E77" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F77" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G77" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H77">
         <v>132240</v>
@@ -15671,10 +15668,10 @@
         <v>75</v>
       </c>
       <c r="E78" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F78" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G78" t="s">
         <v>853</v>
@@ -15697,13 +15694,13 @@
         <v>76</v>
       </c>
       <c r="E79" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F79" t="s">
         <v>564</v>
       </c>
       <c r="G79" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H79">
         <v>3400</v>
@@ -15729,7 +15726,7 @@
         <v>547</v>
       </c>
       <c r="G80" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H80">
         <v>128320</v>
@@ -15752,10 +15749,10 @@
         <v>1358</v>
       </c>
       <c r="F81" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G81" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H81">
         <v>84590</v>
@@ -15775,10 +15772,10 @@
         <v>79</v>
       </c>
       <c r="E82" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F82" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G82" t="s">
         <v>983</v>
@@ -15801,13 +15798,13 @@
         <v>80</v>
       </c>
       <c r="E83" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F83" t="s">
         <v>643</v>
       </c>
       <c r="G83" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H83">
         <v>29400</v>
@@ -15827,13 +15824,13 @@
         <v>81</v>
       </c>
       <c r="E84" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F84" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G84" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H84">
         <v>32230</v>
@@ -15853,13 +15850,13 @@
         <v>82</v>
       </c>
       <c r="E85" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F85" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G85" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H85">
         <v>30450</v>
@@ -15879,13 +15876,13 @@
         <v>83</v>
       </c>
       <c r="E86" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F86" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G86" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H86">
         <v>22700</v>
@@ -15908,10 +15905,10 @@
         <v>1358</v>
       </c>
       <c r="F87" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G87" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H87">
         <v>28240</v>
@@ -15931,13 +15928,13 @@
         <v>85</v>
       </c>
       <c r="E88" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F88" t="s">
         <v>670</v>
       </c>
       <c r="G88" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H88">
         <v>35320</v>
@@ -15960,10 +15957,10 @@
         <v>1358</v>
       </c>
       <c r="F89" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G89" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H89">
         <v>168460</v>
@@ -15983,13 +15980,13 @@
         <v>87</v>
       </c>
       <c r="E90" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F90" t="s">
         <v>554</v>
       </c>
       <c r="G90" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H90">
         <v>42830</v>
@@ -16012,7 +16009,7 @@
         <v>1358</v>
       </c>
       <c r="F91" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="G91" t="s">
         <v>748</v>
@@ -16035,7 +16032,7 @@
         <v>89</v>
       </c>
       <c r="E92" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F92" t="s">
         <v>575</v>
@@ -16113,13 +16110,13 @@
         <v>92</v>
       </c>
       <c r="E95" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F95" t="s">
         <v>545</v>
       </c>
       <c r="G95" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H95">
         <v>56230</v>
@@ -16139,7 +16136,7 @@
         <v>93</v>
       </c>
       <c r="E96" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F96" t="s">
         <v>544</v>
@@ -16165,7 +16162,7 @@
         <v>94</v>
       </c>
       <c r="E97" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F97" t="s">
         <v>495</v>
@@ -16191,10 +16188,10 @@
         <v>95</v>
       </c>
       <c r="E98" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F98" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G98" t="s">
         <v>808</v>
@@ -16223,7 +16220,7 @@
         <v>646</v>
       </c>
       <c r="G99" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H99">
         <v>164020</v>
@@ -16243,10 +16240,10 @@
         <v>97</v>
       </c>
       <c r="E100" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F100" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G100" t="s">
         <v>813</v>
@@ -16269,13 +16266,13 @@
         <v>98</v>
       </c>
       <c r="E101" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F101" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G101" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H101">
         <v>96460</v>
@@ -16295,7 +16292,7 @@
         <v>99</v>
       </c>
       <c r="E102" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F102" t="s">
         <v>738</v>
@@ -16327,7 +16324,7 @@
         <v>680</v>
       </c>
       <c r="G103" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H103">
         <v>318960</v>
@@ -16347,13 +16344,13 @@
         <v>101</v>
       </c>
       <c r="E104" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F104" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G104" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H104">
         <v>241200</v>
@@ -16373,7 +16370,7 @@
         <v>102</v>
       </c>
       <c r="E105" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F105" t="s">
         <v>492</v>
@@ -16399,13 +16396,13 @@
         <v>103</v>
       </c>
       <c r="E106" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F106" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G106" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H106">
         <v>203000</v>
@@ -16425,13 +16422,13 @@
         <v>104</v>
       </c>
       <c r="E107" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F107" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G107" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H107">
         <v>65000</v>
@@ -16451,13 +16448,13 @@
         <v>105</v>
       </c>
       <c r="E108" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F108" t="s">
         <v>501</v>
       </c>
       <c r="G108" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H108">
         <v>153557</v>
@@ -16480,7 +16477,7 @@
         <v>1358</v>
       </c>
       <c r="F109" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G109" t="s">
         <v>962</v>
@@ -16506,7 +16503,7 @@
         <v>1358</v>
       </c>
       <c r="F110" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="G110" t="s">
         <v>962</v>
@@ -16529,7 +16526,7 @@
         <v>108</v>
       </c>
       <c r="E111" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F111" t="s">
         <v>575</v>
@@ -16555,7 +16552,7 @@
         <v>109</v>
       </c>
       <c r="E112" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F112" t="s">
         <v>575</v>
@@ -16581,7 +16578,7 @@
         <v>110</v>
       </c>
       <c r="E113" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F113" t="s">
         <v>575</v>
@@ -16607,10 +16604,10 @@
         <v>111</v>
       </c>
       <c r="E114" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F114" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G114" t="s">
         <v>808</v>
@@ -16633,10 +16630,10 @@
         <v>112</v>
       </c>
       <c r="E115" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F115" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G115" t="s">
         <v>935</v>
@@ -16659,7 +16656,7 @@
         <v>113</v>
       </c>
       <c r="E116" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F116" t="s">
         <v>695</v>
@@ -16685,7 +16682,7 @@
         <v>114</v>
       </c>
       <c r="E117" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F117" t="s">
         <v>683</v>
@@ -16711,13 +16708,13 @@
         <v>115</v>
       </c>
       <c r="E118" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F118" t="s">
         <v>545</v>
       </c>
       <c r="G118" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H118">
         <v>31320</v>
@@ -16737,7 +16734,7 @@
         <v>116</v>
       </c>
       <c r="E119" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F119" t="s">
         <v>495</v>
@@ -16763,13 +16760,13 @@
         <v>117</v>
       </c>
       <c r="E120" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F120" t="s">
         <v>495</v>
       </c>
       <c r="G120" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H120">
         <v>1000000</v>
@@ -16789,7 +16786,7 @@
         <v>118</v>
       </c>
       <c r="E121" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F121" t="s">
         <v>544</v>
@@ -16815,7 +16812,7 @@
         <v>119</v>
       </c>
       <c r="E122" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F122" t="s">
         <v>495</v>
@@ -16841,7 +16838,7 @@
         <v>120</v>
       </c>
       <c r="E123" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F123" t="s">
         <v>738</v>
@@ -16867,13 +16864,13 @@
         <v>121</v>
       </c>
       <c r="E124" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F124" t="s">
         <v>646</v>
       </c>
       <c r="G124" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H124">
         <v>40000</v>
@@ -16893,10 +16890,10 @@
         <v>122</v>
       </c>
       <c r="E125" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F125" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G125" t="s">
         <v>813</v>
@@ -16919,7 +16916,7 @@
         <v>123</v>
       </c>
       <c r="E126" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F126" t="s">
         <v>654</v>
@@ -16945,13 +16942,13 @@
         <v>124</v>
       </c>
       <c r="E127" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F127" t="s">
         <v>496</v>
       </c>
       <c r="G127" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H127">
         <v>77550</v>
@@ -16971,7 +16968,7 @@
         <v>125</v>
       </c>
       <c r="E128" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F128" t="s">
         <v>492</v>
@@ -16997,7 +16994,7 @@
         <v>126</v>
       </c>
       <c r="E129" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F129" t="s">
         <v>497</v>
@@ -17023,7 +17020,7 @@
         <v>127</v>
       </c>
       <c r="E130" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F130" t="s">
         <v>688</v>
@@ -17049,7 +17046,7 @@
         <v>128</v>
       </c>
       <c r="E131" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F131" t="s">
         <v>503</v>
@@ -17075,7 +17072,7 @@
         <v>129</v>
       </c>
       <c r="E132" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F132" t="s">
         <v>575</v>
@@ -17101,7 +17098,7 @@
         <v>130</v>
       </c>
       <c r="E133" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F133" t="s">
         <v>492</v>
@@ -17127,13 +17124,13 @@
         <v>131</v>
       </c>
       <c r="E134" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F134" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G134" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H134">
         <v>62640</v>
@@ -17153,13 +17150,13 @@
         <v>132</v>
       </c>
       <c r="E135" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F135" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G135" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H135">
         <v>114840</v>
@@ -17205,7 +17202,7 @@
         <v>134</v>
       </c>
       <c r="E137" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F137" t="s">
         <v>717</v>
@@ -17231,7 +17228,7 @@
         <v>135</v>
       </c>
       <c r="E138" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F138" t="s">
         <v>634</v>
@@ -17257,7 +17254,7 @@
         <v>136</v>
       </c>
       <c r="E139" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F139" t="s">
         <v>634</v>
@@ -17283,7 +17280,7 @@
         <v>137</v>
       </c>
       <c r="E140" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F140" t="s">
         <v>599</v>
@@ -17309,7 +17306,7 @@
         <v>138</v>
       </c>
       <c r="E141" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F141" t="s">
         <v>598</v>
@@ -17335,7 +17332,7 @@
         <v>139</v>
       </c>
       <c r="E142" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F142" t="s">
         <v>604</v>
@@ -17361,7 +17358,7 @@
         <v>140</v>
       </c>
       <c r="E143" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F143" t="s">
         <v>599</v>
@@ -17387,10 +17384,10 @@
         <v>141</v>
       </c>
       <c r="E144" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F144" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G144" t="s">
         <v>880</v>
@@ -17413,7 +17410,7 @@
         <v>142</v>
       </c>
       <c r="E145" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F145" t="s">
         <v>599</v>
@@ -17439,7 +17436,7 @@
         <v>143</v>
       </c>
       <c r="E146" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F146" t="s">
         <v>632</v>
@@ -17465,7 +17462,7 @@
         <v>144</v>
       </c>
       <c r="E147" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F147" t="s">
         <v>603</v>
@@ -17491,7 +17488,7 @@
         <v>145</v>
       </c>
       <c r="E148" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F148" t="s">
         <v>599</v>
@@ -17517,13 +17514,13 @@
         <v>146</v>
       </c>
       <c r="E149" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F149" t="s">
         <v>601</v>
       </c>
       <c r="G149" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H149">
         <v>56000</v>
@@ -17543,13 +17540,13 @@
         <v>147</v>
       </c>
       <c r="E150" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F150" t="s">
         <v>638</v>
       </c>
       <c r="G150" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H150">
         <v>69008</v>
@@ -17569,10 +17566,10 @@
         <v>148</v>
       </c>
       <c r="E151" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F151" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G151" t="s">
         <v>753</v>
@@ -17595,13 +17592,13 @@
         <v>149</v>
       </c>
       <c r="E152" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F152" t="s">
         <v>603</v>
       </c>
       <c r="G152" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H152">
         <v>72800</v>
@@ -17621,10 +17618,10 @@
         <v>150</v>
       </c>
       <c r="E153" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F153" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G153" t="s">
         <v>889</v>
@@ -17647,7 +17644,7 @@
         <v>151</v>
       </c>
       <c r="E154" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F154" t="s">
         <v>626</v>
@@ -17673,7 +17670,7 @@
         <v>152</v>
       </c>
       <c r="E155" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F155" t="s">
         <v>601</v>
@@ -17699,7 +17696,7 @@
         <v>153</v>
       </c>
       <c r="E156" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F156" t="s">
         <v>614</v>
@@ -17725,7 +17722,7 @@
         <v>154</v>
       </c>
       <c r="E157" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F157" t="s">
         <v>601</v>
@@ -17751,7 +17748,7 @@
         <v>155</v>
       </c>
       <c r="E158" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F158" t="s">
         <v>714</v>
@@ -17777,7 +17774,7 @@
         <v>156</v>
       </c>
       <c r="E159" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F159" t="s">
         <v>619</v>
@@ -17803,7 +17800,7 @@
         <v>157</v>
       </c>
       <c r="E160" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F160" t="s">
         <v>626</v>
@@ -17829,7 +17826,7 @@
         <v>158</v>
       </c>
       <c r="E161" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F161" t="s">
         <v>599</v>
@@ -17855,13 +17852,13 @@
         <v>159</v>
       </c>
       <c r="E162" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F162" t="s">
         <v>599</v>
       </c>
       <c r="G162" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H162">
         <v>81000</v>
@@ -17881,7 +17878,7 @@
         <v>160</v>
       </c>
       <c r="E163" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F163" t="s">
         <v>619</v>
@@ -17907,7 +17904,7 @@
         <v>161</v>
       </c>
       <c r="E164" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F164" t="s">
         <v>619</v>
@@ -17933,7 +17930,7 @@
         <v>162</v>
       </c>
       <c r="E165" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F165" t="s">
         <v>717</v>
@@ -17959,7 +17956,7 @@
         <v>163</v>
       </c>
       <c r="E166" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F166" t="s">
         <v>616</v>
@@ -17985,10 +17982,10 @@
         <v>164</v>
       </c>
       <c r="E167" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F167" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G167" t="s">
         <v>862</v>
@@ -18011,7 +18008,7 @@
         <v>165</v>
       </c>
       <c r="E168" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F168" t="s">
         <v>624</v>
@@ -18037,7 +18034,7 @@
         <v>166</v>
       </c>
       <c r="E169" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F169" t="s">
         <v>601</v>
@@ -18063,7 +18060,7 @@
         <v>167</v>
       </c>
       <c r="E170" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F170" t="s">
         <v>619</v>
@@ -18089,7 +18086,7 @@
         <v>168</v>
       </c>
       <c r="E171" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F171" t="s">
         <v>637</v>
@@ -18115,13 +18112,13 @@
         <v>169</v>
       </c>
       <c r="E172" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F172" t="s">
         <v>630</v>
       </c>
       <c r="G172" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H172">
         <v>30590</v>
@@ -18167,7 +18164,7 @@
         <v>171</v>
       </c>
       <c r="E174" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F174" t="s">
         <v>623</v>
@@ -18193,7 +18190,7 @@
         <v>172</v>
       </c>
       <c r="E175" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F175" t="s">
         <v>610</v>
@@ -18219,13 +18216,13 @@
         <v>173</v>
       </c>
       <c r="E176" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F176" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G176" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H176">
         <v>58700</v>
@@ -18245,7 +18242,7 @@
         <v>174</v>
       </c>
       <c r="E177" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F177" t="s">
         <v>639</v>
@@ -18271,7 +18268,7 @@
         <v>175</v>
       </c>
       <c r="E178" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F178" t="s">
         <v>626</v>
@@ -18297,13 +18294,13 @@
         <v>176</v>
       </c>
       <c r="E179" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F179" t="s">
         <v>723</v>
       </c>
       <c r="G179" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H179">
         <v>100000</v>
@@ -18323,13 +18320,13 @@
         <v>177</v>
       </c>
       <c r="E180" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F180" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G180" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H180">
         <v>65100</v>
@@ -18349,13 +18346,13 @@
         <v>178</v>
       </c>
       <c r="E181" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F181" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G181" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H181">
         <v>42700</v>
@@ -18375,7 +18372,7 @@
         <v>179</v>
       </c>
       <c r="E182" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F182" t="s">
         <v>635</v>
@@ -18401,7 +18398,7 @@
         <v>180</v>
       </c>
       <c r="E183" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F183" t="s">
         <v>635</v>
@@ -18427,13 +18424,13 @@
         <v>181</v>
       </c>
       <c r="E184" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F184" t="s">
         <v>604</v>
       </c>
       <c r="G184" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H184">
         <v>28000</v>
@@ -18453,13 +18450,13 @@
         <v>182</v>
       </c>
       <c r="E185" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F185" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G185" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H185">
         <v>34500</v>
@@ -18479,7 +18476,7 @@
         <v>183</v>
       </c>
       <c r="E186" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F186" t="s">
         <v>604</v>
@@ -18505,10 +18502,10 @@
         <v>184</v>
       </c>
       <c r="E187" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F187" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G187" t="s">
         <v>990</v>
@@ -18531,7 +18528,7 @@
         <v>185</v>
       </c>
       <c r="E188" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F188" t="s">
         <v>624</v>
@@ -18557,13 +18554,13 @@
         <v>186</v>
       </c>
       <c r="E189" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F189" t="s">
         <v>716</v>
       </c>
       <c r="G189" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H189">
         <v>102420</v>
@@ -18583,10 +18580,10 @@
         <v>187</v>
       </c>
       <c r="E190" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F190" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G190" t="s">
         <v>977</v>
@@ -18609,13 +18606,13 @@
         <v>188</v>
       </c>
       <c r="E191" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F191" t="s">
         <v>612</v>
       </c>
       <c r="G191" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H191">
         <v>71700</v>
@@ -18635,7 +18632,7 @@
         <v>189</v>
       </c>
       <c r="E192" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F192" t="s">
         <v>611</v>
@@ -18661,13 +18658,13 @@
         <v>190</v>
       </c>
       <c r="E193" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F193" t="s">
         <v>616</v>
       </c>
       <c r="G193" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H193">
         <v>40400</v>
@@ -18687,13 +18684,13 @@
         <v>191</v>
       </c>
       <c r="E194" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F194" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G194" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H194">
         <v>52400</v>
@@ -18713,7 +18710,7 @@
         <v>192</v>
       </c>
       <c r="E195" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F195" t="s">
         <v>598</v>
@@ -18739,7 +18736,7 @@
         <v>193</v>
       </c>
       <c r="E196" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F196" t="s">
         <v>617</v>
@@ -18765,13 +18762,13 @@
         <v>194</v>
       </c>
       <c r="E197" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F197" t="s">
         <v>723</v>
       </c>
       <c r="G197" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H197">
         <v>58800</v>
@@ -18791,10 +18788,10 @@
         <v>195</v>
       </c>
       <c r="E198" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F198" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G198" t="s">
         <v>977</v>
@@ -18817,13 +18814,13 @@
         <v>196</v>
       </c>
       <c r="E199" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F199" t="s">
         <v>600</v>
       </c>
       <c r="G199" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H199">
         <v>61600</v>
@@ -18843,13 +18840,13 @@
         <v>197</v>
       </c>
       <c r="E200" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F200" t="s">
         <v>600</v>
       </c>
       <c r="G200" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H200">
         <v>61600</v>
@@ -18869,7 +18866,7 @@
         <v>198</v>
       </c>
       <c r="E201" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F201" t="s">
         <v>610</v>
@@ -18895,7 +18892,7 @@
         <v>199</v>
       </c>
       <c r="E202" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F202" t="s">
         <v>604</v>
@@ -18921,13 +18918,13 @@
         <v>200</v>
       </c>
       <c r="E203" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F203" t="s">
         <v>723</v>
       </c>
       <c r="G203" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H203">
         <v>51600</v>
@@ -18947,10 +18944,10 @@
         <v>201</v>
       </c>
       <c r="E204" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F204" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G204" t="s">
         <v>755</v>
@@ -18973,13 +18970,13 @@
         <v>202</v>
       </c>
       <c r="E205" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F205" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G205" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H205">
         <v>144014.5</v>
@@ -18999,13 +18996,13 @@
         <v>203</v>
       </c>
       <c r="E206" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F206" t="s">
         <v>733</v>
       </c>
       <c r="G206" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H206">
         <v>81500</v>
@@ -19025,13 +19022,13 @@
         <v>204</v>
       </c>
       <c r="E207" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F207" t="s">
         <v>733</v>
       </c>
       <c r="G207" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H207">
         <v>94100</v>
@@ -19051,13 +19048,13 @@
         <v>205</v>
       </c>
       <c r="E208" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F208" t="s">
         <v>733</v>
       </c>
       <c r="G208" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H208">
         <v>40300</v>
@@ -19077,13 +19074,13 @@
         <v>206</v>
       </c>
       <c r="E209" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F209" t="s">
         <v>631</v>
       </c>
       <c r="G209" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H209">
         <v>30800</v>
@@ -19103,10 +19100,10 @@
         <v>207</v>
       </c>
       <c r="E210" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F210" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G210" t="s">
         <v>753</v>
@@ -19129,13 +19126,13 @@
         <v>208</v>
       </c>
       <c r="E211" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F211" t="s">
         <v>623</v>
       </c>
       <c r="G211" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H211">
         <v>44800</v>
@@ -19155,13 +19152,13 @@
         <v>209</v>
       </c>
       <c r="E212" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F212" t="s">
         <v>623</v>
       </c>
       <c r="G212" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H212">
         <v>81200</v>
@@ -19181,7 +19178,7 @@
         <v>210</v>
       </c>
       <c r="E213" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F213" t="s">
         <v>604</v>
@@ -19207,7 +19204,7 @@
         <v>211</v>
       </c>
       <c r="E214" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F214" t="s">
         <v>601</v>
@@ -19233,7 +19230,7 @@
         <v>212</v>
       </c>
       <c r="E215" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F215" t="s">
         <v>603</v>
@@ -19259,7 +19256,7 @@
         <v>213</v>
       </c>
       <c r="E216" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F216" t="s">
         <v>626</v>
@@ -19285,13 +19282,13 @@
         <v>214</v>
       </c>
       <c r="E217" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F217" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G217" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H217">
         <v>67200</v>
@@ -19311,13 +19308,13 @@
         <v>215</v>
       </c>
       <c r="E218" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F218" t="s">
         <v>616</v>
       </c>
       <c r="G218" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H218">
         <v>56000</v>
@@ -19337,13 +19334,13 @@
         <v>216</v>
       </c>
       <c r="E219" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F219" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G219" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H219">
         <v>84000</v>
@@ -19363,7 +19360,7 @@
         <v>217</v>
       </c>
       <c r="E220" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F220" t="s">
         <v>634</v>
@@ -19389,13 +19386,13 @@
         <v>218</v>
       </c>
       <c r="E221" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F221" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G221" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H221">
         <v>67200</v>
@@ -19415,13 +19412,13 @@
         <v>219</v>
       </c>
       <c r="E222" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F222" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G222" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H222">
         <v>50400</v>
@@ -19441,13 +19438,13 @@
         <v>220</v>
       </c>
       <c r="E223" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F223" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G223" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H223">
         <v>50400</v>
@@ -19467,7 +19464,7 @@
         <v>221</v>
       </c>
       <c r="E224" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F224" t="s">
         <v>599</v>
@@ -19493,7 +19490,7 @@
         <v>222</v>
       </c>
       <c r="E225" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F225" t="s">
         <v>604</v>
@@ -19519,7 +19516,7 @@
         <v>223</v>
       </c>
       <c r="E226" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F226" t="s">
         <v>614</v>
@@ -19545,7 +19542,7 @@
         <v>224</v>
       </c>
       <c r="E227" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F227" t="s">
         <v>604</v>
@@ -19571,7 +19568,7 @@
         <v>225</v>
       </c>
       <c r="E228" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F228" t="s">
         <v>614</v>
@@ -19597,10 +19594,10 @@
         <v>226</v>
       </c>
       <c r="E229" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F229" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G229" t="s">
         <v>755</v>
@@ -19623,7 +19620,7 @@
         <v>227</v>
       </c>
       <c r="E230" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F230" t="s">
         <v>717</v>
@@ -19649,7 +19646,7 @@
         <v>228</v>
       </c>
       <c r="E231" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F231" t="s">
         <v>717</v>
@@ -19675,10 +19672,10 @@
         <v>229</v>
       </c>
       <c r="E232" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F232" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G232" t="s">
         <v>862</v>
@@ -19701,7 +19698,7 @@
         <v>230</v>
       </c>
       <c r="E233" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F233" t="s">
         <v>720</v>
@@ -19727,13 +19724,13 @@
         <v>231</v>
       </c>
       <c r="E234" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F234" t="s">
         <v>635</v>
       </c>
       <c r="G234" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H234">
         <v>61600</v>
@@ -19753,13 +19750,13 @@
         <v>232</v>
       </c>
       <c r="E235" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F235" t="s">
         <v>723</v>
       </c>
       <c r="G235" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H235">
         <v>100000</v>
@@ -19779,13 +19776,13 @@
         <v>233</v>
       </c>
       <c r="E236" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F236" t="s">
         <v>733</v>
       </c>
       <c r="G236" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H236">
         <v>77000</v>
@@ -19805,13 +19802,13 @@
         <v>234</v>
       </c>
       <c r="E237" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F237" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G237" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H237">
         <v>34500</v>
@@ -19831,7 +19828,7 @@
         <v>235</v>
       </c>
       <c r="E238" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F238" t="s">
         <v>603</v>
@@ -19857,7 +19854,7 @@
         <v>236</v>
       </c>
       <c r="E239" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F239" t="s">
         <v>603</v>
@@ -19883,7 +19880,7 @@
         <v>237</v>
       </c>
       <c r="E240" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F240" t="s">
         <v>716</v>
@@ -19909,7 +19906,7 @@
         <v>238</v>
       </c>
       <c r="E241" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F241" t="s">
         <v>630</v>
@@ -19935,7 +19932,7 @@
         <v>239</v>
       </c>
       <c r="E242" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F242" t="s">
         <v>623</v>
@@ -19961,13 +19958,13 @@
         <v>240</v>
       </c>
       <c r="E243" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F243" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G243" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H243">
         <v>100000</v>
@@ -19987,7 +19984,7 @@
         <v>241</v>
       </c>
       <c r="E244" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F244" t="s">
         <v>731</v>
@@ -20013,13 +20010,13 @@
         <v>242</v>
       </c>
       <c r="E245" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F245" t="s">
         <v>600</v>
       </c>
       <c r="G245" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H245">
         <v>73500</v>
@@ -20039,7 +20036,7 @@
         <v>243</v>
       </c>
       <c r="E246" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F246" t="s">
         <v>631</v>
@@ -20065,7 +20062,7 @@
         <v>244</v>
       </c>
       <c r="E247" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F247" t="s">
         <v>637</v>
@@ -20091,10 +20088,10 @@
         <v>245</v>
       </c>
       <c r="E248" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F248" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G248" t="s">
         <v>897</v>
@@ -20117,7 +20114,7 @@
         <v>246</v>
       </c>
       <c r="E249" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F249" t="s">
         <v>638</v>
@@ -20143,7 +20140,7 @@
         <v>247</v>
       </c>
       <c r="E250" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F250" t="s">
         <v>634</v>
@@ -20169,7 +20166,7 @@
         <v>248</v>
       </c>
       <c r="E251" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F251" t="s">
         <v>622</v>
@@ -20195,7 +20192,7 @@
         <v>249</v>
       </c>
       <c r="E252" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F252" t="s">
         <v>730</v>
@@ -20221,10 +20218,10 @@
         <v>250</v>
       </c>
       <c r="E253" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F253" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G253" t="s">
         <v>972</v>
@@ -20247,7 +20244,7 @@
         <v>251</v>
       </c>
       <c r="E254" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F254" t="s">
         <v>733</v>
@@ -20273,7 +20270,7 @@
         <v>252</v>
       </c>
       <c r="E255" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F255" t="s">
         <v>617</v>
@@ -20299,13 +20296,13 @@
         <v>253</v>
       </c>
       <c r="E256" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F256" t="s">
         <v>732</v>
       </c>
       <c r="G256" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H256">
         <v>50000</v>
@@ -20325,7 +20322,7 @@
         <v>254</v>
       </c>
       <c r="E257" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F257" t="s">
         <v>617</v>
@@ -20351,13 +20348,13 @@
         <v>255</v>
       </c>
       <c r="E258" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F258" t="s">
         <v>630</v>
       </c>
       <c r="G258" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H258">
         <v>50000</v>
@@ -20377,13 +20374,13 @@
         <v>256</v>
       </c>
       <c r="E259" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F259" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G259" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H259">
         <v>70536.35000000001</v>
@@ -20429,13 +20426,13 @@
         <v>258</v>
       </c>
       <c r="E261" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F261" t="s">
         <v>660</v>
       </c>
       <c r="G261" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -20455,7 +20452,7 @@
         <v>259</v>
       </c>
       <c r="E262" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F262" t="s">
         <v>679</v>
@@ -20481,13 +20478,13 @@
         <v>260</v>
       </c>
       <c r="E263" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F263" t="s">
         <v>574</v>
       </c>
       <c r="G263" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H263">
         <v>38521.5</v>
@@ -20559,7 +20556,7 @@
         <v>263</v>
       </c>
       <c r="E266" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F266" t="s">
         <v>568</v>
@@ -20585,7 +20582,7 @@
         <v>264</v>
       </c>
       <c r="E267" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F267" t="s">
         <v>704</v>
@@ -20611,13 +20608,13 @@
         <v>265</v>
       </c>
       <c r="E268" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F268" t="s">
         <v>704</v>
       </c>
       <c r="G268" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H268">
         <v>30281</v>
@@ -20663,7 +20660,7 @@
         <v>267</v>
       </c>
       <c r="E270" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F270" t="s">
         <v>485</v>
@@ -20689,13 +20686,13 @@
         <v>268</v>
       </c>
       <c r="E271" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F271" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G271" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H271">
         <v>136801.41</v>
@@ -20715,13 +20712,13 @@
         <v>269</v>
       </c>
       <c r="E272" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F272" t="s">
         <v>674</v>
       </c>
       <c r="G272" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H272">
         <v>183750</v>
@@ -20741,13 +20738,13 @@
         <v>270</v>
       </c>
       <c r="E273" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F273" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G273" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H273">
         <v>25200</v>
@@ -20767,13 +20764,13 @@
         <v>271</v>
       </c>
       <c r="E274" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F274" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G274" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H274">
         <v>25200</v>
@@ -20793,13 +20790,13 @@
         <v>272</v>
       </c>
       <c r="E275" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F275" t="s">
         <v>574</v>
       </c>
       <c r="G275" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H275">
         <v>134400</v>
@@ -20819,7 +20816,7 @@
         <v>273</v>
       </c>
       <c r="E276" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F276" t="s">
         <v>661</v>
@@ -20845,13 +20842,13 @@
         <v>274</v>
       </c>
       <c r="E277" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F277" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G277" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H277">
         <v>39000</v>
